--- a/etc/hebrew/proper_nouns.xlsx
+++ b/etc/hebrew/proper_nouns.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -668,6 +668,48 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Yoram Bronowski</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>יוֹרָם בְּרוֹנוֹבְסְקִי</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Plato</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>אַפְּלָטוֹן</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/proper_nouns.xlsx
+++ b/etc/hebrew/proper_nouns.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -710,6 +710,174 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>דָּן</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Ofra</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>עוֹפְרָה</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>proper noun; source spelling: עופרה</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>חֵן</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>proper noun; unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Yossi</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>יוֹסִי</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Hannah</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>חַנָּה</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Churchill</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>צֶ'רְצִ'יל</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>George</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>ג'וֹרְג'</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>רִיוֹ דֶה זַ'נֵרוֹ</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>proper noun; source spelling: ריו דה ז׳נרו</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/proper_nouns.xlsx
+++ b/etc/hebrew/proper_nouns.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>צֶ'רְצִ'יל</t>
+          <t>צֶ׳רְצִ׳יל</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -844,7 +844,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ג'וֹרְג'</t>
+          <t>ג׳וֹרְג׳</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
@@ -869,7 +869,7 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>רִיוֹ דֶה זַ'נֵרוֹ</t>
+          <t>רִיוֹ דֶה זַ׳נֵרוֹ</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">

--- a/etc/hebrew/proper_nouns.xlsx
+++ b/etc/hebrew/proper_nouns.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -878,6 +878,111 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>בּוֹסְטוֹן</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>proper noun; source spelling: בוסטון</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Donald Trump</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>דּוֹנַלְד טְרַמְפּ</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>proper noun; source spelling: דונלד טרמפ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Starbucks</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>סְטַרְבַּקְס</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>proper noun; source spelling: סטרבקס</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Times Square</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>טַיימְס סְקְוֶור</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>proper noun; source spelling: טיימס סקוור</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Dani</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>דָּנִי</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/proper_nouns.xlsx
+++ b/etc/hebrew/proper_nouns.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -983,6 +983,27 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Yom Hazikaron; Memorial Day</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>יוֹם הַזִּכָּרוֹן</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>proper noun; source spelling: יום הזיכרון</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/proper_nouns.xlsx
+++ b/etc/hebrew/proper_nouns.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1004,6 +1004,69 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Galit</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>גָּלִית</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Shula</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>שׁוּלָה</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Miriam</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>מִרְיָם</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
